--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -4220,7 +4220,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 39.9, "op_wape_pct": 99.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 173.53, "rev_act": 137.05, "op_pred": -1.18, "op_act": 11.6}, {"q": "2025Q4", "rev_pred": 303.02, "rev_act": 165.06, "op_pred": -2.06, "op_act": -18.69}, {"q": "2026Q1", "rev_pred": 100.73, "rev_act": 75.62, "op_pred": -0.68, "op_act": -16.05}, {"q": "2026Q2", "rev_pred": 151.69, "rev_act": 143.5, "op_pred": -1.03, "op_act": 11.18}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 39.9, "op_wape_pct": 99.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 173.53, "rev_act": 137.05, "op_pred": -1.18, "op_act": 11.6}, {"q": "2025Q4", "rev_pred": 303.02, "rev_act": 165.06, "op_pred": -2.06, "op_act": -18.69}, {"q": "2026Q1", "rev_pred": 100.73, "rev_act": 75.62, "op_pred": -0.68, "op_act": -16.05}, {"q": "2026Q2", "rev_pred": 151.69, "rev_act": 143.5, "op_pred": -1.03, "op_act": 11.18}]}</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2565</v>
+        <v>2555</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5795,7 +5795,7 @@
         <v>2960</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>2585</v>
+        <v>2600</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2545</v>
+        <v>2548.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2565</v>
+        <v>2555</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.03362195070025523</v>
+        <v>0.03362195070025463</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02363633724654358</v>
+        <v>0.0236363372465433</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35566,7 +35566,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2555</v>
+        <v>2535</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5795,7 +5795,7 @@
         <v>2960</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>2600</v>
+        <v>2850</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2548.3</v>
+        <v>2547.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,11 +8420,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2555</v>
+        <v>2535</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,530원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,555원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35566,7 +35566,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2535</v>
+        <v>2490</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2547.5</v>
+        <v>2535</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,11 +8420,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2535</v>
+        <v>2490</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,555원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,550원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35566,7 +35566,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.03362195070025463</v>
+        <v>0.03362195070025523</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.0236363372465433</v>
+        <v>0.02363633724654358</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2490</v>
+        <v>2485</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,11 +8420,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2490</v>
+        <v>2485</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,550원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,580원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.03362195070025523</v>
+        <v>0.03362195070025463</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02363633724654358</v>
+        <v>0.0236363372465433</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2485</v>
+        <v>2345</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5886,7 +5886,7 @@
         <v>1767</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2435</v>
+        <v>2300</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2534</v>
+        <v>2502.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2485</v>
+        <v>2345</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35566,7 +35566,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2345</v>
+        <v>2290</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5886,7 +5886,7 @@
         <v>1767</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2300</v>
+        <v>2235</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2502.5</v>
+        <v>2474.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,11 +8420,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2345</v>
+        <v>2290</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,580원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,495원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35566,7 +35566,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2290</v>
+        <v>2325</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2474.3</v>
+        <v>2457.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,11 +8420,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2290</v>
+        <v>2325</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,495원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,375원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35566,7 +35566,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2325</v>
+        <v>2290</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5886,7 +5886,7 @@
         <v>1767</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2235</v>
+        <v>2095</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2457.5</v>
+        <v>2392.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,11 +8420,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2325</v>
+        <v>2290</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,375원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,185원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35566,7 +35566,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/011700_model.xlsx
+++ b/argus/kship/models/011700_model.xlsx
@@ -3865,7 +3865,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4736,35 +4736,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4855,35 +4855,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4974,35 +4974,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5093,35 +5093,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5212,35 +5212,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5331,35 +5331,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5450,35 +5450,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5569,35 +5569,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5704,7 +5704,7 @@
         <v>2455</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2290</v>
+        <v>2065</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5886,7 +5886,7 @@
         <v>1767</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2095</v>
+        <v>2050</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>2421.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2392.7</v>
+        <v>2315.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8420,11 +8420,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2290</v>
+        <v>2065</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,185원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,160원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35566,7 +35566,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="33">
